--- a/docs/处理学习记录.xlsx
+++ b/docs/处理学习记录.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12165"/>
+    <workbookView windowWidth="28800" windowHeight="11715" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="expose功能" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
   <si>
     <t>根据bond 和component已有的方程，来写这个方程式</t>
   </si>
@@ -198,6 +199,54 @@
   </si>
   <si>
     <t>采用SUNDIALS套件求解这个函数</t>
+  </si>
+  <si>
+    <t>1、expose前</t>
+  </si>
+  <si>
+    <t>num(model.inter_ports)=14，num(model.ports)=0</t>
+  </si>
+  <si>
+    <t>2、expose时</t>
+  </si>
+  <si>
+    <t>(1)、判断是否"SS"</t>
+  </si>
+  <si>
+    <t>(2)、不是则创建一个ss,加入model</t>
+  </si>
+  <si>
+    <t>num(model.inter_ports)=15，num(model.ports)=0</t>
+  </si>
+  <si>
+    <t>(3)connect ss到expose的component上</t>
+  </si>
+  <si>
+    <t>（3.1） 对于compnent上,可能增加了一个port</t>
+  </si>
+  <si>
+    <t>num(model.inter_ports)=16，num(model.ports)=0</t>
+  </si>
+  <si>
+    <t>（3.2）连接两个创建第15 和16个port</t>
+  </si>
+  <si>
+    <t>(3.3) 将bond 加入model</t>
+  </si>
+  <si>
+    <t>(4)为model.ports中map_port 1个</t>
+  </si>
+  <si>
+    <t>(4.1)这个label找的到port，就将ef写入</t>
+  </si>
+  <si>
+    <t>（4.2）找不到就创建一个新的port，需要给定一个index 和1个port_name</t>
+  </si>
+  <si>
+    <t>num(model.inter_ports)=16，num(model.ports)=1</t>
+  </si>
+  <si>
+    <t>创建1个interport,1个ports 就行？？</t>
   </si>
 </sst>
 </file>
@@ -614,19 +663,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color auto="1"/>
@@ -648,6 +684,19 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -898,7 +947,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -909,16 +958,22 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -932,20 +987,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1478,12 +1524,12 @@
     <col min="2" max="2" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2">
+    <row r="2" spans="1:19">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:16">
+    <row r="3" spans="1:19">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="E3" s="2" t="s">
@@ -1501,7 +1547,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="2:17">
+    <row r="4" spans="1:19">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" t="s">
@@ -1531,11 +1577,11 @@
         <v>8</v>
       </c>
       <c r="P4" s="3"/>
-      <c r="Q4" s="12" t="s">
+      <c r="Q4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:17">
+    <row r="5" spans="1:19">
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
         <v>10</v>
@@ -1579,56 +1625,56 @@
       <c r="P5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="Q5" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:19">
+    <row r="6" spans="1:19">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="4">
+      <c r="D6" s="6">
         <v>0</v>
       </c>
-      <c r="E6" s="5">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
         <v>2</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="7">
         <v>3</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="7">
         <v>4</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="7">
         <v>5</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="7">
         <v>6</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="7">
         <v>7</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="7">
         <v>8</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="7">
         <v>9</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="7">
         <v>10</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="7">
         <v>11</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="7">
         <v>12</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="Q6" s="8">
         <v>13</v>
       </c>
-      <c r="R6" s="4"/>
+      <c r="R6" s="6"/>
       <c r="S6" t="s">
         <v>25</v>
       </c>
@@ -1637,181 +1683,181 @@
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="10">
         <v>0</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10">
-        <v>1</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10">
+      <c r="D7" s="11"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12">
+        <v>1</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12">
         <v>-1</v>
       </c>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="4" t="s">
+      <c r="P7" s="12"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="S7" s="15"/>
+      <c r="S7" s="13"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10">
-        <v>1</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="4" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="10">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12">
+        <v>1</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="S8" s="15"/>
+      <c r="S8" s="13"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="10">
         <v>2</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10">
+      <c r="D9" s="11"/>
+      <c r="E9" s="12">
         <v>-1</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10">
-        <v>1</v>
-      </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="11"/>
-      <c r="S9" s="15"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12">
+        <v>1</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="14"/>
+      <c r="S9" s="13"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8">
+      <c r="B10" s="9"/>
+      <c r="C10" s="10">
         <v>3</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="11"/>
-      <c r="S10" s="15"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12">
+        <v>1</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12">
+        <v>1</v>
+      </c>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="14"/>
+      <c r="S10" s="13"/>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="10">
         <v>4</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10">
-        <v>1</v>
-      </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10">
+      <c r="D11" s="11"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12">
+        <v>1</v>
+      </c>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12">
         <v>-1</v>
       </c>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="11"/>
-      <c r="S11" s="15"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="14"/>
+      <c r="S11" s="13"/>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8">
+      <c r="B12" s="9"/>
+      <c r="C12" s="10">
         <v>5</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10">
-        <v>1</v>
-      </c>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10">
-        <v>1</v>
-      </c>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="11"/>
-      <c r="S12" s="15"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12">
+        <v>1</v>
+      </c>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12">
+        <v>1</v>
+      </c>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="14"/>
+      <c r="S12" s="13"/>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="6" t="s">
@@ -1820,28 +1866,28 @@
       <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="10">
         <v>6</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="11">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9">
+      <c r="D13" s="11"/>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11">
         <v>-1</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="S13" s="15"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="S13" s="13"/>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="6">
@@ -1850,28 +1896,28 @@
       <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="10">
         <v>7</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9">
-        <v>1</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9">
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11">
+        <v>1</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11">
         <v>-1</v>
       </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="S14" s="15"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="S14" s="13"/>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="6">
@@ -1880,28 +1926,28 @@
       <c r="B15" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="10">
         <v>8</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9">
-        <v>1</v>
-      </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9">
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11">
+        <v>1</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11">
         <v>-1</v>
       </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="S15" s="15"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="S15" s="13"/>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="6">
@@ -1910,30 +1956,30 @@
       <c r="B16" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="10">
         <v>9</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9">
-        <v>1</v>
-      </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9">
-        <v>1</v>
-      </c>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9">
-        <v>1</v>
-      </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="S16" s="15"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11">
+        <v>1</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11">
+        <v>1</v>
+      </c>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11">
+        <v>1</v>
+      </c>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="S16" s="13"/>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="6" t="s">
@@ -1942,28 +1988,28 @@
       <c r="B17" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="10">
         <v>10</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9">
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11">
         <v>-1</v>
       </c>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9">
-        <v>1</v>
-      </c>
-      <c r="S17" s="15"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11">
+        <v>1</v>
+      </c>
+      <c r="S17" s="13"/>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="6" t="s">
@@ -1972,28 +2018,28 @@
       <c r="B18" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="10">
         <v>11</v>
       </c>
-      <c r="D18" s="9">
-        <v>1</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9">
+      <c r="D18" s="11">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11">
         <v>-1</v>
       </c>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="S18" s="15"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="S18" s="13"/>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="6" t="s">
@@ -2002,40 +2048,40 @@
       <c r="B19" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="10">
         <v>12</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9">
-        <v>1</v>
-      </c>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="S19" s="15">
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11">
+        <v>1</v>
+      </c>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="S19" s="13">
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="18:18">
+    <row r="20" spans="1:19">
       <c r="R20" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
+    <row r="24" spans="1:19">
       <c r="B24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
+    <row r="25" spans="1:19">
       <c r="B25" t="s">
         <v>45</v>
       </c>
@@ -2043,52 +2089,52 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="3:3">
+    <row r="26" spans="1:19">
       <c r="C26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:2">
+    <row r="27" spans="1:19">
       <c r="B27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="2:2">
+    <row r="29" spans="1:19">
       <c r="B29" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="3:3">
+    <row r="30" spans="1:19">
       <c r="C30" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" spans="1:19">
       <c r="B31" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="1:19">
       <c r="B32" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="3:3">
+    <row r="33" spans="2:3">
       <c r="C33" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:3">
       <c r="B34" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="3:3">
+    <row r="35" spans="2:3">
       <c r="C35" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="3:3">
+    <row r="36" spans="2:3">
       <c r="C36" t="s">
         <v>56</v>
       </c>
@@ -2102,4 +2148,91 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B2:C19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="19.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>